--- a/output/details/2026-05-14/preprocessed_data.xlsx
+++ b/output/details/2026-05-14/preprocessed_data.xlsx
@@ -15231,25 +15231,25 @@
         <v>46156</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1091360783488448</v>
+        <v>-0.1097899582508998</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1785479416996804</v>
+        <v>-0.1406259679492204</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1782951446358161</v>
+        <v>-0.1403492291827732</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1304512198865881</v>
+        <v>0.004578667871976015</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001702820224443399</v>
+        <v>0.001702309679115294</v>
       </c>
       <c r="G2" t="n">
-        <v>1.848440587690744</v>
+        <v>2.432659791020588</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.453229451327668</v>
+        <v>-0.2619862208506732</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
